--- a/resultados_log.xlsx
+++ b/resultados_log.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pesos óptimos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retornos esperados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medidas de riesgo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pesos óptimos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Retornos esperados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Medidas de riesgo" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.6768</v>
+        <v>2.3446</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9937</v>
+        <v>2.783</v>
       </c>
       <c r="D2" t="n">
-        <v>16.8534</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>16.863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2048</v>
+        <v>5.0522</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.009399999999999</v>
+        <v>8.0197</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.7222</v>
+        <v>5.7434</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4204</v>
+        <v>5.442</v>
       </c>
       <c r="D5" t="n">
-        <v>23.0261</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>23.0113</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.2323</v>
+        <v>7.7997</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4192</v>
+        <v>1.5058</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3602</v>
+        <v>1.2532</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2324</v>
+        <v>1.236</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -578,29 +578,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6799</v>
+        <v>2.5216</v>
       </c>
       <c r="C8" t="n">
-        <v>2.7232</v>
+        <v>2.7471</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3911</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3509</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDN</t>
+          <t>ECOG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.228</v>
+        <v>1.1326</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0291</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -612,14 +612,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GGAL</t>
+          <t>EDN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.0428</v>
+        <v>1.2239</v>
       </c>
       <c r="C10" t="n">
-        <v>4.35</v>
+        <v>1.0219</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -631,14 +631,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOMA</t>
+          <t>GGAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4749</v>
+        <v>14.0616</v>
       </c>
       <c r="C11" t="n">
-        <v>3.3031</v>
+        <v>2.3942</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -650,14 +650,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>METR</t>
+          <t>LOMA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8689</v>
+        <v>3.0278</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1778</v>
+        <v>2.7631</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -669,17 +669,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAMP</t>
+          <t>METR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14.6787</v>
+        <v>0.8203</v>
       </c>
       <c r="C13" t="n">
-        <v>25.194</v>
+        <v>0.1025</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -688,14 +688,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUPV</t>
+          <t>PAMP</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7442</v>
+        <v>12.3259</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>26.8935</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -707,14 +707,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TECO2</t>
+          <t>SUPV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1948</v>
+        <v>2.4136</v>
       </c>
       <c r="C15" t="n">
-        <v>2.1516</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1663</v>
+        <v>1.4223</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1001</v>
+        <v>1.5301</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6422</v>
+        <v>5.661</v>
       </c>
       <c r="C17" t="n">
-        <v>12.9651</v>
+        <v>13.0294</v>
       </c>
       <c r="D17" t="n">
-        <v>6.037</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6.5132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2265</v>
+        <v>1.7552</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2847</v>
+        <v>2.0418</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>28.139</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>27.7643</v>
       </c>
     </row>
     <row r="19">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.0218</v>
+        <v>3.9582</v>
       </c>
       <c r="C19" t="n">
-        <v>5.02</v>
+        <v>3.9401</v>
       </c>
       <c r="D19" t="n">
-        <v>4.6619</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2791</v>
+        <v>2.0699</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4001</v>
+        <v>2.5697</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>10.5341</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>10.523</v>
       </c>
     </row>
     <row r="21">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.5463</v>
+        <v>17.3932</v>
       </c>
       <c r="C21" t="n">
-        <v>29.2354</v>
+        <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>15.8831</v>
+        <v>1.3269</v>
       </c>
       <c r="E21" t="n">
-        <v>15.5934</v>
+        <v>1.7127</v>
       </c>
     </row>
     <row r="22">
@@ -914,22 +914,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.142781</v>
+        <v>0.137835</v>
       </c>
       <c r="C2" t="n">
-        <v>35.9807</v>
+        <v>34.7344</v>
       </c>
       <c r="D2" t="n">
-        <v>0.218208</v>
+        <v>0.034769</v>
       </c>
       <c r="E2" t="n">
-        <v>54.9884</v>
+        <v>8.761799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.218312</v>
+        <v>0.035188</v>
       </c>
       <c r="G2" t="n">
-        <v>55.0146</v>
+        <v>8.8674</v>
       </c>
     </row>
     <row r="3">
@@ -939,22 +939,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.245038</v>
+        <v>0.240345</v>
       </c>
       <c r="C3" t="n">
-        <v>61.7495</v>
+        <v>60.567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.221724</v>
+        <v>-0.015533</v>
       </c>
       <c r="E3" t="n">
-        <v>55.8746</v>
+        <v>-3.9144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.221485</v>
+        <v>-0.015279</v>
       </c>
       <c r="G3" t="n">
-        <v>55.8142</v>
+        <v>-3.8502</v>
       </c>
     </row>
     <row r="4">
@@ -964,22 +964,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.247734</v>
+        <v>0.242152</v>
       </c>
       <c r="C4" t="n">
-        <v>62.4289</v>
+        <v>61.0223</v>
       </c>
       <c r="D4" t="n">
-        <v>0.217434</v>
+        <v>0.003995</v>
       </c>
       <c r="E4" t="n">
-        <v>54.7935</v>
+        <v>1.0067</v>
       </c>
       <c r="F4" t="n">
-        <v>0.217032</v>
+        <v>0.00438</v>
       </c>
       <c r="G4" t="n">
-        <v>54.6921</v>
+        <v>1.1038</v>
       </c>
     </row>
     <row r="5">
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.164649</v>
+        <v>0.162813</v>
       </c>
       <c r="C5" t="n">
-        <v>41.4917</v>
+        <v>41.029</v>
       </c>
       <c r="D5" t="n">
-        <v>0.238292</v>
+        <v>0.15238</v>
       </c>
       <c r="E5" t="n">
-        <v>60.0495</v>
+        <v>38.3997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.238387</v>
+        <v>0.152059</v>
       </c>
       <c r="G5" t="n">
-        <v>60.0735</v>
+        <v>38.3189</v>
       </c>
     </row>
     <row r="6">
@@ -1014,22 +1014,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.239298</v>
+        <v>0.235604</v>
       </c>
       <c r="C6" t="n">
-        <v>60.303</v>
+        <v>59.3723</v>
       </c>
       <c r="D6" t="n">
-        <v>0.204527</v>
+        <v>0.126589</v>
       </c>
       <c r="E6" t="n">
-        <v>51.5407</v>
+        <v>31.9005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.204713</v>
+        <v>0.126782</v>
       </c>
       <c r="G6" t="n">
-        <v>51.5876</v>
+        <v>31.9491</v>
       </c>
     </row>
     <row r="7">
@@ -1039,22 +1039,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.161065</v>
+        <v>0.162744</v>
       </c>
       <c r="C7" t="n">
-        <v>40.5884</v>
+        <v>41.0114</v>
       </c>
       <c r="D7" t="n">
-        <v>0.202814</v>
+        <v>-0.239959</v>
       </c>
       <c r="E7" t="n">
-        <v>51.1092</v>
+        <v>-60.4696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.202888</v>
+        <v>-0.241046</v>
       </c>
       <c r="G7" t="n">
-        <v>51.1278</v>
+        <v>-60.7435</v>
       </c>
     </row>
     <row r="8">
@@ -1064,197 +1064,197 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.185415</v>
+        <v>0.181534</v>
       </c>
       <c r="C8" t="n">
-        <v>46.7247</v>
+        <v>45.7465</v>
       </c>
       <c r="D8" t="n">
-        <v>0.211651</v>
+        <v>0.102171</v>
       </c>
       <c r="E8" t="n">
-        <v>53.3362</v>
+        <v>25.7471</v>
       </c>
       <c r="F8" t="n">
-        <v>0.211696</v>
+        <v>0.102622</v>
       </c>
       <c r="G8" t="n">
-        <v>53.3475</v>
+        <v>25.8608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EDN</t>
+          <t>ECOG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.220323</v>
+        <v>0.204406</v>
       </c>
       <c r="C9" t="n">
-        <v>55.5215</v>
+        <v>51.5102</v>
       </c>
       <c r="D9" t="n">
-        <v>0.192018</v>
+        <v>0.047883</v>
       </c>
       <c r="E9" t="n">
-        <v>48.3886</v>
+        <v>12.0665</v>
       </c>
       <c r="F9" t="n">
-        <v>0.192141</v>
+        <v>0.046458</v>
       </c>
       <c r="G9" t="n">
-        <v>48.4196</v>
+        <v>11.7073</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GGAL</t>
+          <t>EDN</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.24245</v>
+        <v>0.219255</v>
       </c>
       <c r="C10" t="n">
-        <v>61.0975</v>
+        <v>55.2523</v>
       </c>
       <c r="D10" t="n">
-        <v>0.225311</v>
+        <v>0.025308</v>
       </c>
       <c r="E10" t="n">
-        <v>56.7783</v>
+        <v>6.3776</v>
       </c>
       <c r="F10" t="n">
-        <v>0.22518</v>
+        <v>0.025505</v>
       </c>
       <c r="G10" t="n">
-        <v>56.7453</v>
+        <v>6.4272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LOMA</t>
+          <t>GGAL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.195515</v>
+        <v>0.237175</v>
       </c>
       <c r="C11" t="n">
-        <v>49.2699</v>
+        <v>59.7682</v>
       </c>
       <c r="D11" t="n">
-        <v>0.188635</v>
+        <v>-0.014346</v>
       </c>
       <c r="E11" t="n">
-        <v>47.536</v>
+        <v>-3.6152</v>
       </c>
       <c r="F11" t="n">
-        <v>0.188713</v>
+        <v>-0.014048</v>
       </c>
       <c r="G11" t="n">
-        <v>47.5557</v>
+        <v>-3.5402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>METR</t>
+          <t>LOMA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.199933</v>
+        <v>0.190347</v>
       </c>
       <c r="C12" t="n">
-        <v>50.3831</v>
+        <v>47.9675</v>
       </c>
       <c r="D12" t="n">
-        <v>0.194</v>
+        <v>0.060674</v>
       </c>
       <c r="E12" t="n">
-        <v>48.8879</v>
+        <v>15.2897</v>
       </c>
       <c r="F12" t="n">
-        <v>0.194162</v>
+        <v>0.061005</v>
       </c>
       <c r="G12" t="n">
-        <v>48.9288</v>
+        <v>15.3733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAMP</t>
+          <t>METR</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.238254</v>
+        <v>0.199559</v>
       </c>
       <c r="C13" t="n">
-        <v>60.04</v>
+        <v>50.2889</v>
       </c>
       <c r="D13" t="n">
-        <v>0.233899</v>
+        <v>-0.045769</v>
       </c>
       <c r="E13" t="n">
-        <v>58.9424</v>
+        <v>-11.5337</v>
       </c>
       <c r="F13" t="n">
-        <v>0.233934</v>
+        <v>-0.046921</v>
       </c>
       <c r="G13" t="n">
-        <v>58.9514</v>
+        <v>-11.8242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUPV</t>
+          <t>PAMP</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.250576</v>
+        <v>0.232604</v>
       </c>
       <c r="C14" t="n">
-        <v>63.1451</v>
+        <v>58.6163</v>
       </c>
       <c r="D14" t="n">
-        <v>0.181388</v>
+        <v>0.095026</v>
       </c>
       <c r="E14" t="n">
-        <v>45.7098</v>
+        <v>23.9465</v>
       </c>
       <c r="F14" t="n">
-        <v>0.181722</v>
+        <v>0.095253</v>
       </c>
       <c r="G14" t="n">
-        <v>45.794</v>
+        <v>24.0038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TECO2</t>
+          <t>SUPV</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.172051</v>
+        <v>0.247178</v>
       </c>
       <c r="C15" t="n">
-        <v>43.3569</v>
+        <v>62.2888</v>
       </c>
       <c r="D15" t="n">
-        <v>0.164301</v>
+        <v>-0.086426</v>
       </c>
       <c r="E15" t="n">
-        <v>41.4039</v>
+        <v>-21.7793</v>
       </c>
       <c r="F15" t="n">
-        <v>0.164296</v>
+        <v>-0.086298</v>
       </c>
       <c r="G15" t="n">
-        <v>41.4026</v>
+        <v>-21.7472</v>
       </c>
     </row>
     <row r="16">
@@ -1264,22 +1264,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.205779</v>
+        <v>0.205169</v>
       </c>
       <c r="C16" t="n">
-        <v>51.8562</v>
+        <v>51.7025</v>
       </c>
       <c r="D16" t="n">
-        <v>0.214056</v>
+        <v>0.135278</v>
       </c>
       <c r="E16" t="n">
-        <v>53.9421</v>
+        <v>34.09</v>
       </c>
       <c r="F16" t="n">
-        <v>0.214216</v>
+        <v>0.133868</v>
       </c>
       <c r="G16" t="n">
-        <v>53.9824</v>
+        <v>33.7347</v>
       </c>
     </row>
     <row r="17">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.235954</v>
+        <v>0.231258</v>
       </c>
       <c r="C17" t="n">
-        <v>59.4605</v>
+        <v>58.2769</v>
       </c>
       <c r="D17" t="n">
-        <v>0.242831</v>
+        <v>0.133804</v>
       </c>
       <c r="E17" t="n">
-        <v>61.1934</v>
+        <v>33.7187</v>
       </c>
       <c r="F17" t="n">
-        <v>0.243355</v>
+        <v>0.134045</v>
       </c>
       <c r="G17" t="n">
-        <v>61.3254</v>
+        <v>33.7793</v>
       </c>
     </row>
     <row r="18">
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.211716</v>
+        <v>0.209766</v>
       </c>
       <c r="C18" t="n">
-        <v>53.3525</v>
+        <v>52.861</v>
       </c>
       <c r="D18" t="n">
-        <v>0.218415</v>
+        <v>0.222598</v>
       </c>
       <c r="E18" t="n">
-        <v>55.0405</v>
+        <v>56.0948</v>
       </c>
       <c r="F18" t="n">
-        <v>0.218601</v>
+        <v>0.221289</v>
       </c>
       <c r="G18" t="n">
-        <v>55.0874</v>
+        <v>55.7647</v>
       </c>
     </row>
     <row r="19">
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.150743</v>
+        <v>0.144643</v>
       </c>
       <c r="C19" t="n">
-        <v>37.9873</v>
+        <v>36.45</v>
       </c>
       <c r="D19" t="n">
-        <v>0.211925</v>
+        <v>-0.047338</v>
       </c>
       <c r="E19" t="n">
-        <v>53.4051</v>
+        <v>-11.9292</v>
       </c>
       <c r="F19" t="n">
-        <v>0.212058</v>
+        <v>-0.047296</v>
       </c>
       <c r="G19" t="n">
-        <v>53.4385</v>
+        <v>-11.9185</v>
       </c>
     </row>
     <row r="20">
@@ -1364,22 +1364,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.131652</v>
+        <v>0.130007</v>
       </c>
       <c r="C20" t="n">
-        <v>33.1762</v>
+        <v>32.7619</v>
       </c>
       <c r="D20" t="n">
-        <v>0.224036</v>
+        <v>0.111537</v>
       </c>
       <c r="E20" t="n">
-        <v>56.4572</v>
+        <v>28.1074</v>
       </c>
       <c r="F20" t="n">
-        <v>0.22409</v>
+        <v>0.111142</v>
       </c>
       <c r="G20" t="n">
-        <v>56.4706</v>
+        <v>28.0078</v>
       </c>
     </row>
     <row r="21">
@@ -1389,22 +1389,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.237273</v>
+        <v>0.232449</v>
       </c>
       <c r="C21" t="n">
-        <v>59.7929</v>
+        <v>58.5771</v>
       </c>
       <c r="D21" t="n">
-        <v>0.242299</v>
+        <v>0.115921</v>
       </c>
       <c r="E21" t="n">
-        <v>61.0594</v>
+        <v>29.2121</v>
       </c>
       <c r="F21" t="n">
-        <v>0.242105</v>
+        <v>0.116051</v>
       </c>
       <c r="G21" t="n">
-        <v>61.0104</v>
+        <v>29.2448</v>
       </c>
     </row>
   </sheetData>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.36236057967607</v>
+        <v>54.30823825341464</v>
       </c>
       <c r="C2" t="n">
-        <v>57.80923905463337</v>
+        <v>38.37704527984319</v>
       </c>
       <c r="D2" t="n">
-        <v>57.83208910423561</v>
+        <v>38.18472821487669</v>
       </c>
     </row>
     <row r="3">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47.22514340942235</v>
+        <v>46.78527812728425</v>
       </c>
       <c r="C3" t="n">
-        <v>40.09708959816887</v>
+        <v>42.08293911824399</v>
       </c>
       <c r="D3" t="n">
-        <v>40.09756456323106</v>
+        <v>41.95878506958353</v>
       </c>
     </row>
     <row r="4">
@@ -1482,13 +1482,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.172306881097373</v>
+        <v>1.160797593329752</v>
       </c>
       <c r="C4" t="n">
-        <v>1.44173154794939</v>
+        <v>0.9119383313986689</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44228433158424</v>
+        <v>0.9100532379941882</v>
       </c>
     </row>
     <row r="5">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.049596436120146</v>
+        <v>4.109660322690196</v>
       </c>
       <c r="C5" t="n">
-        <v>3.424623177085182</v>
+        <v>4.158001247009068</v>
       </c>
       <c r="D5" t="n">
-        <v>3.422493895048857</v>
+        <v>4.122042509383903</v>
       </c>
     </row>
     <row r="6">
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.518105783669751</v>
+        <v>5.558253355942537</v>
       </c>
       <c r="C6" t="n">
-        <v>5.648153850248434</v>
+        <v>5.350605563222064</v>
       </c>
       <c r="D6" t="n">
-        <v>5.648608268933793</v>
+        <v>5.338281049251489</v>
       </c>
     </row>
     <row r="7">
@@ -1530,13 +1530,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.35297148945207</v>
+        <v>7.092150254359689</v>
       </c>
       <c r="C7" t="n">
-        <v>6.328445312042247</v>
+        <v>5.73854010850253</v>
       </c>
       <c r="D7" t="n">
-        <v>6.329498091591708</v>
+        <v>5.728701341152616</v>
       </c>
     </row>
     <row r="8">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.19106291833493</v>
+        <v>9.766429101068255</v>
       </c>
       <c r="C8" t="n">
-        <v>10.49204490622705</v>
+        <v>7.773972928499962</v>
       </c>
       <c r="D8" t="n">
-        <v>10.49104789180261</v>
+        <v>7.785503706678252</v>
       </c>
     </row>
   </sheetData>
